--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4039,8 +4146,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4059,992 +4170,999 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">양산도 — 민요채보-2/양산도.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">양산도</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 姑</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="13"/>
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="14"/>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="14"/>
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="15"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 姑</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="O5" s="15"/>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">놓</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">놓</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K6" s="13"/>
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 姑</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="14"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="14"/>
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 姑</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="C8" s="15"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 姑</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">봇</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="G9" s="13"/>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="14"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="E10" s="14"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="14"/>
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M10" s="14"/>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢
 姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E11" s="15"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="15"/>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="15"/>
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="15"/>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="13"/>
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="M12" s="13"/>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 黃</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="G13" s="14"/>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="K13" s="14"/>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="14"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞
 潢</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -1092,13 +1092,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -1528,13 +1528,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3188,7 +3188,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3253,7 +3253,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3302,7 +3302,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="9"/>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3513,7 +3513,7 @@
       <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -3532,7 +3532,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="10"/>
@@ -3565,7 +3565,7 @@
       <c r="L8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="M8" s="10"/>
@@ -3699,7 +3699,7 @@
       <c r="I11" s="10"/>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K11" s="10"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3148,94 +3189,94 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">양산도</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="E3" s="24"/>
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="G3" s="24"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙
 姑</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">옴</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">덕</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3243,45 +3284,45 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 僙
@@ -3289,31 +3330,31 @@
 仲</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲
 汰</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3321,67 +3362,67 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="28"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
-      <c r="N5" s="17"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="N5" s="21"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -3389,187 +3430,187 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">놈</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">맹</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="M8" s="27"/>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
@@ -3577,35 +3618,35 @@
 姑</t>
         </is>
       </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="O8" s="28"/>
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q8" s="13"/>
+      <c r="Q8" s="28"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 仲
@@ -3613,226 +3654,226 @@
 仲</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南
 南</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="12"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="K11" s="27"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="M11" s="13" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">옴</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="18" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">／
 △</t>
         </is>
       </c>
-      <c r="Q13" s="12"/>
+      <c r="Q13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -3166,28 +3166,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="Q8" s="28"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="25"/>
@@ -3688,7 +3688,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="25"/>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="27"/>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Q11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Q12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="25"/>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Q13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="27"/>
@@ -3864,7 +3864,7 @@
       <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="27"/>

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3218,7 +3241,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -3226,14 +3249,14 @@
 仲</t>
         </is>
       </c>
-      <c r="E3" s="24"/>
+      <c r="E3" s="30"/>
       <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="30"/>
       <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
@@ -3241,7 +3264,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">옴</t>
         </is>
@@ -3251,20 +3274,20 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="29"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="29"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">덕</t>
         </is>
@@ -3276,7 +3299,7 @@
 無</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3291,14 +3314,14 @@
 仲</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -3310,7 +3333,7 @@
 南</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3321,7 +3344,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
@@ -3330,7 +3353,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -3340,13 +3363,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
@@ -3354,7 +3377,7 @@
 汰</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3369,13 +3392,13 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -3387,7 +3410,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -3397,32 +3420,32 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="28"/>
+      <c r="I5" s="34"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K5" s="27"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
       <c r="N5" s="21"/>
-      <c r="O5" s="27"/>
+      <c r="O5" s="33"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -3437,13 +3460,13 @@
 仲</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
@@ -3453,7 +3476,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">놈</t>
         </is>
@@ -3463,7 +3486,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
@@ -3473,7 +3496,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3483,7 +3506,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3493,7 +3516,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">맹</t>
         </is>
@@ -3503,7 +3526,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q6" s="22"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
@@ -3512,23 +3535,23 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="21"/>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3539,14 +3562,14 @@
 仲</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3557,7 +3580,7 @@
 –無</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -3567,7 +3590,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
     </row>
     <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
@@ -3576,15 +3599,15 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="21"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -3592,7 +3615,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3602,14 +3625,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="33"/>
       <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -3618,34 +3641,34 @@
 姑</t>
         </is>
       </c>
-      <c r="O8" s="28"/>
+      <c r="O8" s="34"/>
       <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q8" s="28"/>
+      <c r="Q8" s="34"/>
     </row>
     <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
+      <c r="G9" s="29"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
@@ -3654,7 +3677,7 @@
 仲</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3666,7 +3689,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="O9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -3676,22 +3699,22 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="29"/>
     </row>
     <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="21"/>
-      <c r="E10" s="25"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="21"/>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -3699,14 +3722,14 @@
 南</t>
         </is>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -3716,7 +3739,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -3726,24 +3749,24 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="26"/>
+      <c r="Q10" s="32"/>
     </row>
     <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="27"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="21"/>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -3751,7 +3774,7 @@
 仲</t>
         </is>
       </c>
-      <c r="M11" s="28" t="inlineStr">
+      <c r="M11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -3762,7 +3785,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O11" s="28" t="inlineStr">
+      <c r="O11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">옴</t>
         </is>
@@ -3772,24 +3795,24 @@
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="34"/>
     </row>
     <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -3799,7 +3822,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3807,31 +3830,31 @@
 無</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="Q12" s="24"/>
+      <c r="Q12" s="30"/>
     </row>
     <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3841,39 +3864,39 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21"/>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">／
 △</t>
         </is>
       </c>
-      <c r="Q13" s="26"/>
+      <c r="Q13" s="32"/>
     </row>
     <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="21"/>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="21"/>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -403,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 –·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네..</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 –·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네.. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -2425,13 +2425,13 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|南|–</t>
+          <t xml:space="preserve">南|姑|–</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-南
+姑
 –</t>
         </is>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-南
+姑
 –</t>
         </is>
       </c>

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -3335,6 +3335,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3351,10 +3354,10 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3373,7 +3376,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3439,7 +3442,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3507,7 +3510,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3561,7 +3564,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3626,7 +3629,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3681,7 +3684,7 @@
       </c>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3729,7 +3732,7 @@
       </c>
       <c r="M8" s="26"/>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3795,7 +3798,7 @@
       </c>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3853,7 +3856,7 @@
       </c>
       <c r="M10" s="25"/>
     </row>
-    <row r="11" ht="77.61" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3905,7 +3908,7 @@
       </c>
       <c r="M11" s="26"/>
     </row>
-    <row r="12" ht="77.61" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3967,7 +3970,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="77.61" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4023,7 +4026,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="77.61" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4082,6 +4085,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/양산도.xlsx
+++ b/sheets/민요/검수/양산도.xlsx
@@ -3340,17 +3340,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
